--- a/public/datos/2.4_Graficos.xlsx
+++ b/public/datos/2.4_Graficos.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Documentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Base_Documentos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Informe_Grafico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,6 +427,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Código de Actividad</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Título del Caso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dashboard visual ejecutivo y reporte de distribución SIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Situación Problema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>El Comité Directivo dispone de solo 5 minutos para evaluar el estado documental. Se requiere un informe gráfico ejecutivo de 1 página con tablas de frecuencias formuladas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Misión del Aprendiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Construir 2 tablas de frecuencias con =CONTAR.SI() en Informe_Grafico y diseñar un Gráfico de Columnas (carga por proceso) y un Gráfico Circular (proporción de estados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Requerimiento 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frecuencias por Proceso: Calcular la cantidad de documentos por proceso con =CONTAR.SI().</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Requerimiento 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Frecuencias por Estado: Calcular cantidad y % de participación por estado (Vigente, Por vencer, Vencido) con =CONTAR.SI().</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Requerimiento 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gráfico de Columnas: Representar la carga documental por proceso con títulos claros y etiquetas numéricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gráfico Circular / Anillos: Representar la proporción de vigencias destacando el sector 'Vencido' en color rojo de alerta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>No se aceptan gráficos generados contando filas manualmente. Sus series deben estar enlazadas a las tablas formuladas con CONTAR.SI().</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1342,20 +1493,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1366,18 +1518,23 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Cantidad de documentos</t>
+          <t>Total Documentos (=CONTAR.SI)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr"/>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Estado Documental</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Cantidad</t>
+          <t>Cantidad (=CONTAR.SI)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>% Participación</t>
         </is>
       </c>
     </row>
